--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/CONNECTICUT_2023.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/CONNECTICUT_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D527"/>
+  <dimension ref="A1:D521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C3">
@@ -410,12 +415,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAJA CALIFORNIA</t>
+          <t>Baja California</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TIJUANA</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="C4">
@@ -426,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C5">
@@ -441,12 +451,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACACOYAGUA</t>
+          <t>Acacoyagua</t>
         </is>
       </c>
       <c r="C6">
@@ -457,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACAPETAHUA</t>
+          <t>Acapetahua</t>
         </is>
       </c>
       <c r="C7">
@@ -470,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMATENANGO DE LA FRONTERA</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C8">
@@ -483,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMATENANGO DEL VALLE</t>
+          <t>Amatenango Del Valle</t>
         </is>
       </c>
       <c r="C9">
@@ -496,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARRIAGA</t>
+          <t>Arriaga</t>
         </is>
       </c>
       <c r="C10">
@@ -509,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BOCHIL</t>
+          <t>Bochil</t>
         </is>
       </c>
       <c r="C11">
@@ -522,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CACAHOATÁN</t>
+          <t>Cacahoatán</t>
         </is>
       </c>
       <c r="C12">
@@ -535,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHAMULA</t>
+          <t>Chamula</t>
         </is>
       </c>
       <c r="C13">
@@ -548,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHILÓN</t>
+          <t>Chilón</t>
         </is>
       </c>
       <c r="C14">
@@ -561,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COMITÁN DE DOMÍNGUEZ</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C15">
@@ -574,9 +629,14 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COPAINALÁ</t>
+          <t>Copainalá</t>
         </is>
       </c>
       <c r="C16">
@@ -587,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EL PORVENIR</t>
+          <t>El Porvenir</t>
         </is>
       </c>
       <c r="C17">
@@ -600,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ESCUINTLA</t>
+          <t>Escuintla</t>
         </is>
       </c>
       <c r="C18">
@@ -613,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FRONTERA COMALAPA</t>
+          <t>Frontera Comalapa</t>
         </is>
       </c>
       <c r="C19">
@@ -626,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HUEHUETÁN</t>
+          <t>Huehuetán</t>
         </is>
       </c>
       <c r="C20">
@@ -639,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HUIXTLA</t>
+          <t>Huixtla</t>
         </is>
       </c>
       <c r="C21">
@@ -652,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JIQUIPILAS</t>
+          <t>Jiquipilas</t>
         </is>
       </c>
       <c r="C22">
@@ -665,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA CONCORDIA</t>
+          <t>La Concordia</t>
         </is>
       </c>
       <c r="C23">
@@ -678,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA GRANDEZA</t>
+          <t>La Grandeza</t>
         </is>
       </c>
       <c r="C24">
@@ -691,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA TRINITARIA</t>
+          <t>La Trinitaria</t>
         </is>
       </c>
       <c r="C25">
@@ -704,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAS MARGARITAS</t>
+          <t>Las Margaritas</t>
         </is>
       </c>
       <c r="C26">
@@ -717,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAS ROSAS</t>
+          <t>Las Rosas</t>
         </is>
       </c>
       <c r="C27">
@@ -730,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MAPASTEPEC</t>
+          <t>Mapastepec</t>
         </is>
       </c>
       <c r="C28">
@@ -743,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MAZAPA DE MADERO</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C29">
@@ -756,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MOTOZINTLA</t>
+          <t>Motozintla</t>
         </is>
       </c>
       <c r="C30">
@@ -769,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OCOSINGO</t>
+          <t>Ocosingo</t>
         </is>
       </c>
       <c r="C31">
@@ -782,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PANTELHÓ</t>
+          <t>Pantelhó</t>
         </is>
       </c>
       <c r="C32">
@@ -795,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PIJIJIAPAN</t>
+          <t>Pijijiapan</t>
         </is>
       </c>
       <c r="C33">
@@ -808,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAN CRISTÓBAL DE LAS CASAS</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C34">
@@ -821,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SILTEPEC</t>
+          <t>Siltepec</t>
         </is>
       </c>
       <c r="C35">
@@ -834,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TAPACHULA</t>
+          <t>Tapachula</t>
         </is>
       </c>
       <c r="C36">
@@ -847,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TAPALAPA</t>
+          <t>Tapalapa</t>
         </is>
       </c>
       <c r="C37">
@@ -860,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TECPATÁN</t>
+          <t>Tecpatán</t>
         </is>
       </c>
       <c r="C38">
@@ -873,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TEOPISCA</t>
+          <t>Teopisca</t>
         </is>
       </c>
       <c r="C39">
@@ -886,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TUMBALÁ</t>
+          <t>Tumbalá</t>
         </is>
       </c>
       <c r="C40">
@@ -899,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TUXTLA CHICO</t>
+          <t>Tuxtla Chico</t>
         </is>
       </c>
       <c r="C41">
@@ -912,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UNIÓN JUÁREZ</t>
+          <t>Unión Juárez</t>
         </is>
       </c>
       <c r="C42">
@@ -925,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VILLA COMALTITLÁN</t>
+          <t>Villa Comaltitlán</t>
         </is>
       </c>
       <c r="C43">
@@ -938,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YAJALÓN</t>
+          <t>Yajalón</t>
         </is>
       </c>
       <c r="C44">
@@ -951,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C45">
@@ -966,12 +1171,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DELICIAS</t>
+          <t>Delicias</t>
         </is>
       </c>
       <c r="C46">
@@ -982,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JUÁREZ</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="C47">
@@ -995,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C48">
@@ -1010,12 +1225,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AZCAPOTZALCO</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="C49">
@@ -1026,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BENITO JUÁREZ</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="C50">
@@ -1039,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COYOACÁN</t>
+          <t>Coyoacán</t>
         </is>
       </c>
       <c r="C51">
@@ -1052,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CUAJIMALPA DE MORELOS</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C52">
@@ -1065,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C53">
@@ -1078,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GUSTAVO A. MADERO</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="C54">
@@ -1091,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IZTACALCO</t>
+          <t>Iztacalco</t>
         </is>
       </c>
       <c r="C55">
@@ -1104,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IZTAPALAPA</t>
+          <t>Iztapalapa</t>
         </is>
       </c>
       <c r="C56">
@@ -1117,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MIGUEL HIDALGO</t>
+          <t>Miguel Hidalgo</t>
         </is>
       </c>
       <c r="C57">
@@ -1130,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>Tlalpan</t>
         </is>
       </c>
       <c r="C58">
@@ -1143,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VENUSTIANO CARRANZA</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="C59">
@@ -1156,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>XOCHIMILCO</t>
+          <t>Xochimilco</t>
         </is>
       </c>
       <c r="C60">
@@ -1169,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ÁLVARO OBREGÓN</t>
+          <t>Álvaro Obregón</t>
         </is>
       </c>
       <c r="C61">
@@ -1182,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C62">
@@ -1197,12 +1477,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>COAHUILA DE ZARAGOZA</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CASTAÑOS</t>
+          <t>Castaños</t>
         </is>
       </c>
       <c r="C63">
@@ -1213,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PIEDRAS NEGRAS</t>
+          <t>Piedras Negras</t>
         </is>
       </c>
       <c r="C64">
@@ -1226,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>San Pedro</t>
         </is>
       </c>
       <c r="C65">
@@ -1239,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TORREÓN</t>
+          <t>Torreón</t>
         </is>
       </c>
       <c r="C66">
@@ -1252,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C67">
@@ -1267,12 +1567,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="C68">
@@ -1283,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GUADALUPE VICTORIA</t>
+          <t>Guadalupe Victoria</t>
         </is>
       </c>
       <c r="C69">
@@ -1296,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C70">
@@ -1311,12 +1621,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ESTADO DE MÉXICO</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ALMOLOYA DE ALQUISIRAS</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C71">
@@ -1327,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AMECAMECA</t>
+          <t>Amecameca</t>
         </is>
       </c>
       <c r="C72">
@@ -1340,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>APAXCO</t>
+          <t>Apaxco</t>
         </is>
       </c>
       <c r="C73">
@@ -1353,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ATIZAPÁN</t>
+          <t>Atizapán</t>
         </is>
       </c>
       <c r="C74">
@@ -1366,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ATIZAPÁN DE ZARAGOZA</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C75">
@@ -1379,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CHALCO</t>
+          <t>Chalco</t>
         </is>
       </c>
       <c r="C76">
@@ -1392,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CHIMALHUACÁN</t>
+          <t>Chimalhuacán</t>
         </is>
       </c>
       <c r="C77">
@@ -1405,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COACALCO DE BERRIOZÁBAL</t>
+          <t>Coacalco De Berriozábal</t>
         </is>
       </c>
       <c r="C78">
@@ -1418,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CUAUTITLÁN</t>
+          <t>Cuautitlán</t>
         </is>
       </c>
       <c r="C79">
@@ -1431,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ECATEPEC DE MORELOS</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C80">
@@ -1444,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EL ORO</t>
+          <t>El Oro</t>
         </is>
       </c>
       <c r="C81">
@@ -1457,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HUEYPOXTLA</t>
+          <t>Hueypoxtla</t>
         </is>
       </c>
       <c r="C82">
@@ -1470,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HUIXQUILUCAN</t>
+          <t>Huixquilucan</t>
         </is>
       </c>
       <c r="C83">
@@ -1483,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>Ixtapaluca</t>
         </is>
       </c>
       <c r="C84">
@@ -1496,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IXTAPAN DE LA SAL</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C85">
@@ -1509,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IXTLAHUACA</t>
+          <t>Ixtlahuaca</t>
         </is>
       </c>
       <c r="C86">
@@ -1522,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JILOTEPEC</t>
+          <t>Jilotepec</t>
         </is>
       </c>
       <c r="C87">
@@ -1535,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JIQUIPILCO</t>
+          <t>Jiquipilco</t>
         </is>
       </c>
       <c r="C88">
@@ -1548,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LA PAZ</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="C89">
@@ -1561,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LERMA</t>
+          <t>Lerma</t>
         </is>
       </c>
       <c r="C90">
@@ -1574,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NAUCALPAN DE JUÁREZ</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C91">
@@ -1587,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NEZAHUALCÓYOTL</t>
+          <t>Nezahualcóyotl</t>
         </is>
       </c>
       <c r="C92">
@@ -1600,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SAN FELIPE DEL PROGRESO</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C93">
@@ -1613,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SULTEPEC</t>
+          <t>Sultepec</t>
         </is>
       </c>
       <c r="C94">
@@ -1626,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TEJUPILCO</t>
+          <t>Tejupilco</t>
         </is>
       </c>
       <c r="C95">
@@ -1639,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TEMASCALCINGO</t>
+          <t>Temascalcingo</t>
         </is>
       </c>
       <c r="C96">
@@ -1652,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TEMASCALTEPEC</t>
+          <t>Temascaltepec</t>
         </is>
       </c>
       <c r="C97">
@@ -1665,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TENANCINGO</t>
+          <t>Tenancingo</t>
         </is>
       </c>
       <c r="C98">
@@ -1678,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TENANGO DEL VALLE</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C99">
@@ -1691,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TEPETLIXPA</t>
+          <t>Tepetlixpa</t>
         </is>
       </c>
       <c r="C100">
@@ -1704,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TEXCALTITLÁN</t>
+          <t>Texcaltitlán</t>
         </is>
       </c>
       <c r="C101">
@@ -1717,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TLALMANALCO</t>
+          <t>Tlalmanalco</t>
         </is>
       </c>
       <c r="C102">
@@ -1730,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA DE BAZ</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C103">
@@ -1743,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TLATLAYA</t>
+          <t>Tlatlaya</t>
         </is>
       </c>
       <c r="C104">
@@ -1756,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TOLUCA</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="C105">
@@ -1769,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TULTEPEC</t>
+          <t>Tultepec</t>
         </is>
       </c>
       <c r="C106">
@@ -1782,9 +2267,14 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VILLA GUERRERO</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C107">
@@ -1795,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VILLA VICTORIA</t>
+          <t>Villa Victoria</t>
         </is>
       </c>
       <c r="C108">
@@ -1808,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ZINACANTEPEC</t>
+          <t>Zinacantepec</t>
         </is>
       </c>
       <c r="C109">
@@ -1821,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C110">
@@ -1836,12 +2341,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ABASOLO</t>
+          <t>Abasolo</t>
         </is>
       </c>
       <c r="C111">
@@ -1852,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>APASEO EL ALTO</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C112">
@@ -1865,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ATARJEA</t>
+          <t>Atarjea</t>
         </is>
       </c>
       <c r="C113">
@@ -1878,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CELAYA</t>
+          <t>Celaya</t>
         </is>
       </c>
       <c r="C114">
@@ -1891,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="C115">
@@ -1904,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IRAPUATO</t>
+          <t>Irapuato</t>
         </is>
       </c>
       <c r="C116">
@@ -1917,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JERÉCUARO</t>
+          <t>Jerécuaro</t>
         </is>
       </c>
       <c r="C117">
@@ -1930,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LEÓN</t>
+          <t>León</t>
         </is>
       </c>
       <c r="C118">
@@ -1943,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MOROLEÓN</t>
+          <t>Moroleón</t>
         </is>
       </c>
       <c r="C119">
@@ -1956,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SALAMANCA</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="C120">
@@ -1969,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SALVATIERRA</t>
+          <t>Salvatierra</t>
         </is>
       </c>
       <c r="C121">
@@ -1982,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SAN FELIPE</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="C122">
@@ -1995,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SAN LUIS DE LA PAZ</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C123">
@@ -2008,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SANTIAGO MARAVATÍO</t>
+          <t>Santiago Maravatío</t>
         </is>
       </c>
       <c r="C124">
@@ -2021,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TIERRA BLANCA</t>
+          <t>Tierra Blanca</t>
         </is>
       </c>
       <c r="C125">
@@ -2034,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YURIRIA</t>
+          <t>Yuriria</t>
         </is>
       </c>
       <c r="C126">
@@ -2047,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C127">
@@ -2062,12 +2647,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ACAPULCO DE JUÁREZ</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C128">
@@ -2078,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ACATEPEC</t>
+          <t>Acatepec</t>
         </is>
       </c>
       <c r="C129">
@@ -2091,9 +2681,14 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AHUACUOTZINGO</t>
+          <t>Ahuacuotzingo</t>
         </is>
       </c>
       <c r="C130">
@@ -2104,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ALCOZAUCA DE GUERRERO</t>
+          <t>Alcozauca De Guerrero</t>
         </is>
       </c>
       <c r="C131">
@@ -2117,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ALPOYECA</t>
+          <t>Alpoyeca</t>
         </is>
       </c>
       <c r="C132">
@@ -2130,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ATOYAC DE ÁLVAREZ</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C133">
@@ -2143,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AYUTLA DE LOS LIBRES</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C134">
@@ -2156,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CHILAPA DE ÁLVAREZ</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C135">
@@ -2169,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>COPANATOYAC</t>
+          <t>Copanatoyac</t>
         </is>
       </c>
       <c r="C136">
@@ -2182,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>COYUCA DE BENÍTEZ</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C137">
@@ -2195,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EDUARDO NERI</t>
+          <t>Eduardo Neri</t>
         </is>
       </c>
       <c r="C138">
@@ -2208,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HUAMUXTITLÁN</t>
+          <t>Huamuxtitlán</t>
         </is>
       </c>
       <c r="C139">
@@ -2221,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IGUALAPA</t>
+          <t>Igualapa</t>
         </is>
       </c>
       <c r="C140">
@@ -2234,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IXCATEOPAN DE CUAUHTÉMOC</t>
+          <t>Ixcateopan De Cuauhtémoc</t>
         </is>
       </c>
       <c r="C141">
@@ -2247,9 +2897,14 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JUAN R. ESCUDERO</t>
+          <t>Juan R. Escudero</t>
         </is>
       </c>
       <c r="C142">
@@ -2260,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>METLATÓNOC</t>
+          <t>Metlatónoc</t>
         </is>
       </c>
       <c r="C143">
@@ -2273,9 +2933,14 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MOCHITLÁN</t>
+          <t>Mochitlán</t>
         </is>
       </c>
       <c r="C144">
@@ -2286,9 +2951,14 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>OLINALÁ</t>
+          <t>Olinalá</t>
         </is>
       </c>
       <c r="C145">
@@ -2299,9 +2969,14 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>OMETEPEC</t>
+          <t>Ometepec</t>
         </is>
       </c>
       <c r="C146">
@@ -2312,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PILCAYA</t>
+          <t>Pilcaya</t>
         </is>
       </c>
       <c r="C147">
@@ -2325,9 +3005,14 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PUNGARABATO</t>
+          <t>Pungarabato</t>
         </is>
       </c>
       <c r="C148">
@@ -2338,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SAN LUIS ACATLÁN</t>
+          <t>San Luis Acatlán</t>
         </is>
       </c>
       <c r="C149">
@@ -2351,9 +3041,14 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="C150">
@@ -2364,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TELOLOAPAN</t>
+          <t>Teloloapan</t>
         </is>
       </c>
       <c r="C151">
@@ -2377,9 +3077,14 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TIXTLA DE GUERRERO</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C152">
@@ -2390,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TLAPA DE COMONFORT</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C153">
@@ -2403,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TLAPEHUALA</t>
+          <t>Tlapehuala</t>
         </is>
       </c>
       <c r="C154">
@@ -2416,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>XALPATLÁHUAC</t>
+          <t>Xalpatláhuac</t>
         </is>
       </c>
       <c r="C155">
@@ -2429,9 +3149,14 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>XOCHIHUEHUETLÁN</t>
+          <t>Xochihuehuetlán</t>
         </is>
       </c>
       <c r="C156">
@@ -2442,9 +3167,14 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ZAPOTITLÁN TABLAS</t>
+          <t>Zapotitlán Tablas</t>
         </is>
       </c>
       <c r="C157">
@@ -2455,9 +3185,14 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C158">
@@ -2470,12 +3205,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ACTOPAN</t>
+          <t>Actopan</t>
         </is>
       </c>
       <c r="C159">
@@ -2486,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>AJACUBA</t>
+          <t>Ajacuba</t>
         </is>
       </c>
       <c r="C160">
@@ -2499,9 +3239,14 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ALFAJAYUCAN</t>
+          <t>Alfajayucan</t>
         </is>
       </c>
       <c r="C161">
@@ -2512,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>APAN</t>
+          <t>Apan</t>
         </is>
       </c>
       <c r="C162">
@@ -2525,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CARDONAL</t>
+          <t>Cardonal</t>
         </is>
       </c>
       <c r="C163">
@@ -2538,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CHAPANTONGO</t>
+          <t>Chapantongo</t>
         </is>
       </c>
       <c r="C164">
@@ -2551,9 +3311,14 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FRANCISCO I. MADERO</t>
+          <t>Francisco I. Madero</t>
         </is>
       </c>
       <c r="C165">
@@ -2564,9 +3329,14 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HUEHUETLA</t>
+          <t>Huehuetla</t>
         </is>
       </c>
       <c r="C166">
@@ -2577,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HUICHAPAN</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C167">
@@ -2590,9 +3365,14 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>IXMIQUILPAN</t>
+          <t>Ixmiquilpan</t>
         </is>
       </c>
       <c r="C168">
@@ -2603,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LOLOTLA</t>
+          <t>Lolotla</t>
         </is>
       </c>
       <c r="C169">
@@ -2616,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>Metepec</t>
         </is>
       </c>
       <c r="C170">
@@ -2629,9 +3419,14 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>METZTITLÁN</t>
+          <t>Metztitlán</t>
         </is>
       </c>
       <c r="C171">
@@ -2642,9 +3437,14 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MINERAL DEL CHICO</t>
+          <t>Mineral Del Chico</t>
         </is>
       </c>
       <c r="C172">
@@ -2655,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MOLANGO DE ESCAMILLA</t>
+          <t>Molango De Escamilla</t>
         </is>
       </c>
       <c r="C173">
@@ -2668,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PACHUCA DE SOTO</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C174">
@@ -2681,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PROGRESO DE OBREGÓN</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C175">
@@ -2694,9 +3509,14 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SAN SALVADOR</t>
+          <t>San Salvador</t>
         </is>
       </c>
       <c r="C176">
@@ -2707,9 +3527,14 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TEPEAPULCO</t>
+          <t>Tepeapulco</t>
         </is>
       </c>
       <c r="C177">
@@ -2720,9 +3545,14 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TIANGUISTENGO</t>
+          <t>Tianguistengo</t>
         </is>
       </c>
       <c r="C178">
@@ -2733,9 +3563,14 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TULA DE ALLENDE</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C179">
@@ -2746,9 +3581,14 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>XOCHICOATLÁN</t>
+          <t>Xochicoatlán</t>
         </is>
       </c>
       <c r="C180">
@@ -2759,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ZACUALTIPÁN DE ÁNGELES</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C181">
@@ -2772,9 +3617,14 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ZEMPOALA</t>
+          <t>Zempoala</t>
         </is>
       </c>
       <c r="C182">
@@ -2785,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ZIMAPÁN</t>
+          <t>Zimapán</t>
         </is>
       </c>
       <c r="C183">
@@ -2798,9 +3653,14 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C184">
@@ -2813,12 +3673,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>JALISCO</t>
+          <t>Jalisco</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>AHUALULCO DE MERCADO</t>
+          <t>Ahualulco De Mercado</t>
         </is>
       </c>
       <c r="C185">
@@ -2829,9 +3689,14 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ATENGO</t>
+          <t>Atengo</t>
         </is>
       </c>
       <c r="C186">
@@ -2842,9 +3707,14 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CUQUÍO</t>
+          <t>Cuquío</t>
         </is>
       </c>
       <c r="C187">
@@ -2855,9 +3725,14 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="C188">
@@ -2868,9 +3743,14 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IXTLAHUACÁN DEL RÍO</t>
+          <t>Ixtlahuacán Del Río</t>
         </is>
       </c>
       <c r="C189">
@@ -2881,9 +3761,14 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LA BARCA</t>
+          <t>La Barca</t>
         </is>
       </c>
       <c r="C190">
@@ -2894,9 +3779,14 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LAGOS DE MORENO</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C191">
@@ -2907,9 +3797,14 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MAGDALENA</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="C192">
@@ -2920,9 +3815,14 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>QUITUPAN</t>
+          <t>Quitupan</t>
         </is>
       </c>
       <c r="C193">
@@ -2933,9 +3833,14 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TAMAZULA DE GORDIANO</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C194">
@@ -2946,9 +3851,14 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TIZAPÁN EL ALTO</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C195">
@@ -2959,9 +3869,14 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TOTOTLÁN</t>
+          <t>Tototlán</t>
         </is>
       </c>
       <c r="C196">
@@ -2972,9 +3887,14 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>VALLE DE JUÁREZ</t>
+          <t>Valle De Juárez</t>
         </is>
       </c>
       <c r="C197">
@@ -2985,9 +3905,14 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ZACOALCO DE TORRES</t>
+          <t>Zacoalco De Torres</t>
         </is>
       </c>
       <c r="C198">
@@ -2998,9 +3923,14 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ZAPOTLÁN EL GRANDE</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C199">
@@ -3011,9 +3941,14 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C200">
@@ -3026,12 +3961,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ANGANGUEO</t>
+          <t>Angangueo</t>
         </is>
       </c>
       <c r="C201">
@@ -3042,9 +3977,14 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>COAHUAYANA</t>
+          <t>Coahuayana</t>
         </is>
       </c>
       <c r="C202">
@@ -3055,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>COTIJA</t>
+          <t>Cotija</t>
         </is>
       </c>
       <c r="C203">
@@ -3068,9 +4013,14 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="C204">
@@ -3081,9 +4031,14 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JIQUILPAN</t>
+          <t>Jiquilpan</t>
         </is>
       </c>
       <c r="C205">
@@ -3094,9 +4049,14 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>LAGUNILLAS</t>
+          <t>Lagunillas</t>
         </is>
       </c>
       <c r="C206">
@@ -3107,9 +4067,14 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>LOS REYES</t>
+          <t>Los Reyes</t>
         </is>
       </c>
       <c r="C207">
@@ -3120,9 +4085,14 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MARCOS CASTELLANOS</t>
+          <t>Marcos Castellanos</t>
         </is>
       </c>
       <c r="C208">
@@ -3133,9 +4103,14 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t>Morelia</t>
         </is>
       </c>
       <c r="C209">
@@ -3146,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PARÁCUARO</t>
+          <t>Parácuaro</t>
         </is>
       </c>
       <c r="C210">
@@ -3159,9 +4139,14 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PERIBÁN</t>
+          <t>Peribán</t>
         </is>
       </c>
       <c r="C211">
@@ -3172,9 +4157,14 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PURUÁNDIRO</t>
+          <t>Puruándiro</t>
         </is>
       </c>
       <c r="C212">
@@ -3185,9 +4175,14 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PÁTZCUARO</t>
+          <t>Pátzcuaro</t>
         </is>
       </c>
       <c r="C213">
@@ -3198,9 +4193,14 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SAHUAYO</t>
+          <t>Sahuayo</t>
         </is>
       </c>
       <c r="C214">
@@ -3211,9 +4211,14 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>TANGAMANDAPIO</t>
+          <t>Tangamandapio</t>
         </is>
       </c>
       <c r="C215">
@@ -3224,9 +4229,14 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>Zamora</t>
         </is>
       </c>
       <c r="C216">
@@ -3237,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ZIRACUARETIRO</t>
+          <t>Ziracuaretiro</t>
         </is>
       </c>
       <c r="C217">
@@ -3250,9 +4265,14 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ZITÁCUARO</t>
+          <t>Zitácuaro</t>
         </is>
       </c>
       <c r="C218">
@@ -3263,9 +4283,14 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C219">
@@ -3278,12 +4303,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>Morelos</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>AXOCHIAPAN</t>
+          <t>Axochiapan</t>
         </is>
       </c>
       <c r="C220">
@@ -3294,9 +4319,14 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>Ayala</t>
         </is>
       </c>
       <c r="C221">
@@ -3307,9 +4337,14 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>CUAUTLA</t>
+          <t>Cuautla</t>
         </is>
       </c>
       <c r="C222">
@@ -3320,9 +4355,14 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CUERNAVACA</t>
+          <t>Cuernavaca</t>
         </is>
       </c>
       <c r="C223">
@@ -3333,9 +4373,14 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JONACATEPEC</t>
+          <t>Jonacatepec</t>
         </is>
       </c>
       <c r="C224">
@@ -3346,9 +4391,14 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TEMOAC</t>
+          <t>Temoac</t>
         </is>
       </c>
       <c r="C225">
@@ -3359,9 +4409,14 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TOTOLAPAN</t>
+          <t>Totolapan</t>
         </is>
       </c>
       <c r="C226">
@@ -3372,9 +4427,14 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YAUTEPEC</t>
+          <t>Yautepec</t>
         </is>
       </c>
       <c r="C227">
@@ -3385,9 +4445,14 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YECAPIXTLA</t>
+          <t>Yecapixtla</t>
         </is>
       </c>
       <c r="C228">
@@ -3398,9 +4463,14 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ZACUALPAN</t>
+          <t>Zacualpan</t>
         </is>
       </c>
       <c r="C229">
@@ -3411,9 +4481,14 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C230">
@@ -3426,12 +4501,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>NAYARIT</t>
+          <t>Nayarit</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>RUÍZ</t>
+          <t>Ruíz</t>
         </is>
       </c>
       <c r="C231">
@@ -3442,9 +4517,14 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C232">
@@ -3457,12 +4537,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>NUEVO LEÓN</t>
+          <t>Nuevo León</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>GUADALUPE</t>
+          <t>Guadalupe</t>
         </is>
       </c>
       <c r="C233">
@@ -3473,9 +4553,14 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MONTEMORELOS</t>
+          <t>Montemorelos</t>
         </is>
       </c>
       <c r="C234">
@@ -3486,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MONTERREY</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="C235">
@@ -3499,9 +4589,14 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C236">
@@ -3514,12 +4609,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ACATLÁN DE PÉREZ FIGUEROA</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C237">
@@ -3530,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ASUNCIÓN CACALOTEPEC</t>
+          <t>Asunción Cacalotepec</t>
         </is>
       </c>
       <c r="C238">
@@ -3543,9 +4643,14 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ASUNCIÓN NOCHIXTLÁN</t>
+          <t>Asunción Nochixtlán</t>
         </is>
       </c>
       <c r="C239">
@@ -3556,9 +4661,14 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>CIÉNEGA DE ZIMATLÁN</t>
+          <t>Ciénega De Zimatlán</t>
         </is>
       </c>
       <c r="C240">
@@ -3569,9 +4679,14 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>CONSTANCIA DEL ROSARIO</t>
+          <t>Constancia Del Rosario</t>
         </is>
       </c>
       <c r="C241">
@@ -3582,9 +4697,14 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HEROICA CIUDAD DE HUAJUAPAN DE LEÓN</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C242">
@@ -3595,9 +4715,14 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HEROICA CIUDAD DE TLAXIACO</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C243">
@@ -3608,9 +4733,14 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HUAJUAPAN DE LEÓN</t>
+          <t>Huajuapan De León</t>
         </is>
       </c>
       <c r="C244">
@@ -3621,9 +4751,14 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>MIAHUATLÁN DE PORFIRIO DÍAZ</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C245">
@@ -3634,9 +4769,14 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>NUEVO ZOQUIÁPAM</t>
+          <t>Nuevo Zoquiápam</t>
         </is>
       </c>
       <c r="C246">
@@ -3647,9 +4787,14 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>OAXACA DE JUÁREZ</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C247">
@@ -3660,9 +4805,14 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>OCOTLÁN DE MORELOS</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C248">
@@ -3673,9 +4823,14 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PINOTEPA DE DON LUIS</t>
+          <t>Pinotepa De Don Luis</t>
         </is>
       </c>
       <c r="C249">
@@ -3686,9 +4841,14 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PUTLA VILLA DE GUERRERO</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C250">
@@ -3699,9 +4859,14 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>REFORMA DE PINEDA</t>
+          <t>Reforma De Pineda</t>
         </is>
       </c>
       <c r="C251">
@@ -3712,9 +4877,14 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SALINA CRUZ</t>
+          <t>Salina Cruz</t>
         </is>
       </c>
       <c r="C252">
@@ -3725,9 +4895,14 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>SAN AGUSTÍN CHAYUCO</t>
+          <t>San Agustín Chayuco</t>
         </is>
       </c>
       <c r="C253">
@@ -3738,9 +4913,14 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SAN AGUSTÍN LOXICHA</t>
+          <t>San Agustín Loxicha</t>
         </is>
       </c>
       <c r="C254">
@@ -3751,9 +4931,14 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SAN AGUSTÍN YATARENI</t>
+          <t>San Agustín Yatareni</t>
         </is>
       </c>
       <c r="C255">
@@ -3764,9 +4949,14 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SAN ANTONINO EL ALTO</t>
+          <t>San Antonino El Alto</t>
         </is>
       </c>
       <c r="C256">
@@ -3777,9 +4967,14 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SAN ANTONINO MONTE VERDE</t>
+          <t>San Antonino Monte Verde</t>
         </is>
       </c>
       <c r="C257">
@@ -3790,9 +4985,14 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE LA CAL</t>
+          <t>San Antonio De La Cal</t>
         </is>
       </c>
       <c r="C258">
@@ -3803,9 +5003,14 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SAN DIONISIO DEL MAR</t>
+          <t>San Dionisio Del Mar</t>
         </is>
       </c>
       <c r="C259">
@@ -3816,9 +5021,14 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO TELIXTLAHUACA</t>
+          <t>San Francisco Telixtlahuaca</t>
         </is>
       </c>
       <c r="C260">
@@ -3829,9 +5039,14 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SAN ILDEFONSO VILLA ALTA</t>
+          <t>San Ildefonso Villa Alta</t>
         </is>
       </c>
       <c r="C261">
@@ -3842,9 +5057,14 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SAN JACINTO TLACOTEPEC</t>
+          <t>San Jacinto Tlacotepec</t>
         </is>
       </c>
       <c r="C262">
@@ -3855,9 +5075,14 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA TUXTEPEC</t>
+          <t>San Juan Bautista Tuxtepec</t>
         </is>
       </c>
       <c r="C263">
@@ -3868,9 +5093,14 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SAN JUAN COLORADO</t>
+          <t>San Juan Colorado</t>
         </is>
       </c>
       <c r="C264">
@@ -3881,9 +5111,14 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SAN JUAN LACHAO</t>
+          <t>San Juan Lachao</t>
         </is>
       </c>
       <c r="C265">
@@ -3894,9 +5129,14 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SAN LORENZO TEXMELÚCAN</t>
+          <t>San Lorenzo Texmelúcan</t>
         </is>
       </c>
       <c r="C266">
@@ -3907,9 +5147,14 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SAN MARTÍN LACHILÁ</t>
+          <t>San Martín Lachilá</t>
         </is>
       </c>
       <c r="C267">
@@ -3920,9 +5165,14 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SAN MIGUEL AMATITLÁN</t>
+          <t>San Miguel Amatitlán</t>
         </is>
       </c>
       <c r="C268">
@@ -3933,9 +5183,14 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SAN MIGUEL DEL PUERTO</t>
+          <t>San Miguel Del Puerto</t>
         </is>
       </c>
       <c r="C269">
@@ -3946,9 +5201,14 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SAN MIGUEL MIXTEPEC</t>
+          <t>San Miguel Mixtepec</t>
         </is>
       </c>
       <c r="C270">
@@ -3959,9 +5219,14 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SAN MIGUEL PANIXTLAHUACA</t>
+          <t>San Miguel Panixtlahuaca</t>
         </is>
       </c>
       <c r="C271">
@@ -3972,9 +5237,14 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SAN MIGUEL SANTA FLOR</t>
+          <t>San Miguel Santa Flor</t>
         </is>
       </c>
       <c r="C272">
@@ -3985,9 +5255,14 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SAN PEDRO ATOYAC</t>
+          <t>San Pedro Atoyac</t>
         </is>
       </c>
       <c r="C273">
@@ -3998,9 +5273,14 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SAN PEDRO COXCALTEPEC CÁNTAROS</t>
+          <t>San Pedro Coxcaltepec Cántaros</t>
         </is>
       </c>
       <c r="C274">
@@ -4011,9 +5291,14 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SAN PEDRO JICAYÁN</t>
+          <t>San Pedro Jicayán</t>
         </is>
       </c>
       <c r="C275">
@@ -4024,9 +5309,14 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SAN PEDRO Y SAN PABLO TEPOSCOLULA</t>
+          <t>San Pedro Y San Pablo Teposcolula</t>
         </is>
       </c>
       <c r="C276">
@@ -4037,9 +5327,14 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SAN RAYMUNDO JALPAN</t>
+          <t>San Raymundo Jalpan</t>
         </is>
       </c>
       <c r="C277">
@@ -4050,9 +5345,14 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SAN SEBASTIÁN TEITIPAC</t>
+          <t>San Sebastián Teitipac</t>
         </is>
       </c>
       <c r="C278">
@@ -4063,9 +5363,14 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SAN SEBASTIÁN TUTLA</t>
+          <t>San Sebastián Tutla</t>
         </is>
       </c>
       <c r="C279">
@@ -4076,9 +5381,14 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>SANTA CATARINA JUQUILA</t>
+          <t>Santa Catarina Juquila</t>
         </is>
       </c>
       <c r="C280">
@@ -4089,9 +5399,14 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SANTA CRUZ MIXTEPEC</t>
+          <t>Santa Cruz Mixtepec</t>
         </is>
       </c>
       <c r="C281">
@@ -4102,9 +5417,14 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SANTA CRUZ XITLA</t>
+          <t>Santa Cruz Xitla</t>
         </is>
       </c>
       <c r="C282">
@@ -4115,9 +5435,14 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SANTA INÉS DEL MONTE</t>
+          <t>Santa Inés Del Monte</t>
         </is>
       </c>
       <c r="C283">
@@ -4128,9 +5453,14 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SANTIAGO CACALOXTEPEC</t>
+          <t>Santiago Cacaloxtepec</t>
         </is>
       </c>
       <c r="C284">
@@ -4141,9 +5471,14 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>SANTIAGO CHAZUMBA</t>
+          <t>Santiago Chazumba</t>
         </is>
       </c>
       <c r="C285">
@@ -4154,9 +5489,14 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>SANTIAGO JAMILTEPEC</t>
+          <t>Santiago Jamiltepec</t>
         </is>
       </c>
       <c r="C286">
@@ -4167,9 +5507,14 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SANTIAGO JUXTLAHUACA</t>
+          <t>Santiago Juxtlahuaca</t>
         </is>
       </c>
       <c r="C287">
@@ -4180,9 +5525,14 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>SANTIAGO PINOTEPA NACIONAL</t>
+          <t>Santiago Pinotepa Nacional</t>
         </is>
       </c>
       <c r="C288">
@@ -4193,9 +5543,14 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>SANTIAGO TETEPEC</t>
+          <t>Santiago Tetepec</t>
         </is>
       </c>
       <c r="C289">
@@ -4206,9 +5561,14 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>SANTIAGO ZACATEPEC</t>
+          <t>Santiago Zacatepec</t>
         </is>
       </c>
       <c r="C290">
@@ -4219,9 +5579,14 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SANTOS REYES NOPALA</t>
+          <t>Santos Reyes Nopala</t>
         </is>
       </c>
       <c r="C291">
@@ -4232,9 +5597,14 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SANTOS REYES TEPEJILLO</t>
+          <t>Santos Reyes Tepejillo</t>
         </is>
       </c>
       <c r="C292">
@@ -4245,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SILACAYOÁPAM</t>
+          <t>Silacayoápam</t>
         </is>
       </c>
       <c r="C293">
@@ -4258,9 +5633,14 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>TEZOATLÁN DE SEGURA Y LUNA</t>
+          <t>Tezoatlán De Segura Y Luna</t>
         </is>
       </c>
       <c r="C294">
@@ -4271,9 +5651,14 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>TLACOLULA DE MATAMOROS</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C295">
@@ -4284,9 +5669,14 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>TLALIXTAC DE CABRERA</t>
+          <t>Tlalixtac De Cabrera</t>
         </is>
       </c>
       <c r="C296">
@@ -4297,9 +5687,14 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>TOTONTEPEC VILLA DE MORELOS</t>
+          <t>Totontepec Villa De Morelos</t>
         </is>
       </c>
       <c r="C297">
@@ -4310,9 +5705,14 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>VILLA DE TUTUTEPEC DE MELCHOR OCAMPO</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C298">
@@ -4323,9 +5723,14 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>VILLA DE ZAACHILA</t>
+          <t>Villa De Zaachila</t>
         </is>
       </c>
       <c r="C299">
@@ -4336,9 +5741,14 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>VILLA HIDALGO</t>
+          <t>Villa Hidalgo</t>
         </is>
       </c>
       <c r="C300">
@@ -4349,9 +5759,14 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>VILLA SOLA DE VEGA</t>
+          <t>Villa Sola De Vega</t>
         </is>
       </c>
       <c r="C301">
@@ -4362,9 +5777,14 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>ZAPOTITLÁN LAGUNAS</t>
+          <t>Zapotitlán Lagunas</t>
         </is>
       </c>
       <c r="C302">
@@ -4375,9 +5795,14 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ZIMATLÁN DE ÁLVAREZ</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C303">
@@ -4388,9 +5813,14 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C304">
@@ -4403,12 +5833,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>ACATLÁN</t>
+          <t>Acatlán</t>
         </is>
       </c>
       <c r="C305">
@@ -4419,9 +5849,14 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>AHUACATLÁN</t>
+          <t>Ahuacatlán</t>
         </is>
       </c>
       <c r="C306">
@@ -4432,9 +5867,14 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>AHUAZOTEPEC</t>
+          <t>Ahuazotepec</t>
         </is>
       </c>
       <c r="C307">
@@ -4445,9 +5885,14 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>AHUEHUETITLA</t>
+          <t>Ahuehuetitla</t>
         </is>
       </c>
       <c r="C308">
@@ -4458,9 +5903,14 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ALBINO ZERTUCHE</t>
+          <t>Albino Zertuche</t>
         </is>
       </c>
       <c r="C309">
@@ -4471,9 +5921,14 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>AMOZOC</t>
+          <t>Amozoc</t>
         </is>
       </c>
       <c r="C310">
@@ -4484,9 +5939,14 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ATLIXCO</t>
+          <t>Atlixco</t>
         </is>
       </c>
       <c r="C311">
@@ -4497,9 +5957,14 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>AXUTLA</t>
+          <t>Axutla</t>
         </is>
       </c>
       <c r="C312">
@@ -4510,9 +5975,14 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>CALPAN</t>
+          <t>Calpan</t>
         </is>
       </c>
       <c r="C313">
@@ -4523,9 +5993,14 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>CALTEPEC</t>
+          <t>Caltepec</t>
         </is>
       </c>
       <c r="C314">
@@ -4536,9 +6011,14 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>CHALCHICOMULA DE SESMA</t>
+          <t>Chalchicomula De Sesma</t>
         </is>
       </c>
       <c r="C315">
@@ -4549,9 +6029,14 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>CHIAUTLA</t>
+          <t>Chiautla</t>
         </is>
       </c>
       <c r="C316">
@@ -4562,9 +6047,14 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>CHIAUTZINGO</t>
+          <t>Chiautzingo</t>
         </is>
       </c>
       <c r="C317">
@@ -4575,9 +6065,14 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>CHIETLA</t>
+          <t>Chietla</t>
         </is>
       </c>
       <c r="C318">
@@ -4588,9 +6083,14 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>CHIGNAHUAPAN</t>
+          <t>Chignahuapan</t>
         </is>
       </c>
       <c r="C319">
@@ -4601,9 +6101,14 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>CHILA</t>
+          <t>Chila</t>
         </is>
       </c>
       <c r="C320">
@@ -4614,9 +6119,14 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>CHILA DE LA SAL</t>
+          <t>Chila De La Sal</t>
         </is>
       </c>
       <c r="C321">
@@ -4627,9 +6137,14 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>CORONANGO</t>
+          <t>Coronango</t>
         </is>
       </c>
       <c r="C322">
@@ -4640,9 +6155,14 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>CUAUTINCHÁN</t>
+          <t>Cuautinchán</t>
         </is>
       </c>
       <c r="C323">
@@ -4653,9 +6173,14 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>CUAUTLANCINGO</t>
+          <t>Cuautlancingo</t>
         </is>
       </c>
       <c r="C324">
@@ -4666,9 +6191,14 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>CUAYUCA DE ANDRADE</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C325">
@@ -4679,9 +6209,14 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>DOMINGO ARENAS</t>
+          <t>Domingo Arenas</t>
         </is>
       </c>
       <c r="C326">
@@ -4692,9 +6227,14 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>EPATLÁN</t>
+          <t>Epatlán</t>
         </is>
       </c>
       <c r="C327">
@@ -4705,9 +6245,14 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>GUADALUPE</t>
+          <t>Guadalupe</t>
         </is>
       </c>
       <c r="C328">
@@ -4718,9 +6263,14 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>GUADALUPE VICTORIA</t>
+          <t>Guadalupe Victoria</t>
         </is>
       </c>
       <c r="C329">
@@ -4731,9 +6281,14 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>HERMENEGILDO GALEANA</t>
+          <t>Hermenegildo Galeana</t>
         </is>
       </c>
       <c r="C330">
@@ -4744,9 +6299,14 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>HUAQUECHULA</t>
+          <t>Huaquechula</t>
         </is>
       </c>
       <c r="C331">
@@ -4757,9 +6317,14 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>HUEHUETLÁN EL GRANDE</t>
+          <t>Huehuetlán El Grande</t>
         </is>
       </c>
       <c r="C332">
@@ -4770,9 +6335,14 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>HUEJOTZINGO</t>
+          <t>Huejotzingo</t>
         </is>
       </c>
       <c r="C333">
@@ -4783,9 +6353,14 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>IZÚCAR DE MATAMOROS</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C334">
@@ -4796,9 +6371,14 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>JUAN C. BONILLA</t>
+          <t>Juan C. Bonilla</t>
         </is>
       </c>
       <c r="C335">
@@ -4809,9 +6389,14 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>LOS REYES DE JUÁREZ</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C336">
@@ -4822,9 +6407,14 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>NEALTICAN</t>
+          <t>Nealtican</t>
         </is>
       </c>
       <c r="C337">
@@ -4835,9 +6425,14 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>NICOLÁS BRAVO</t>
+          <t>Nicolás Bravo</t>
         </is>
       </c>
       <c r="C338">
@@ -4848,9 +6443,14 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>OCOYUCAN</t>
+          <t>Ocoyucan</t>
         </is>
       </c>
       <c r="C339">
@@ -4861,9 +6461,14 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PALMAR DE BRAVO</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C340">
@@ -4874,9 +6479,14 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PETLALCINGO</t>
+          <t>Petlalcingo</t>
         </is>
       </c>
       <c r="C341">
@@ -4887,9 +6497,14 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PIAXTLA</t>
+          <t>Piaxtla</t>
         </is>
       </c>
       <c r="C342">
@@ -4900,9 +6515,14 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C343">
@@ -4913,9 +6533,14 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS CHOLULA</t>
+          <t>San Andrés Cholula</t>
         </is>
       </c>
       <c r="C344">
@@ -4926,9 +6551,14 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>SAN FELIPE TEOTLALCINGO</t>
+          <t>San Felipe Teotlalcingo</t>
         </is>
       </c>
       <c r="C345">
@@ -4939,9 +6569,14 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>SAN GREGORIO ATZOMPA</t>
+          <t>San Gregorio Atzompa</t>
         </is>
       </c>
       <c r="C346">
@@ -4952,9 +6587,14 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>SAN JERÓNIMO TECUANIPAN</t>
+          <t>San Jerónimo Tecuanipan</t>
         </is>
       </c>
       <c r="C347">
@@ -4965,9 +6605,14 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>SAN JERÓNIMO XAYACATLÁN</t>
+          <t>San Jerónimo Xayacatlán</t>
         </is>
       </c>
       <c r="C348">
@@ -4978,9 +6623,14 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>SAN JUAN ATZOMPA</t>
+          <t>San Juan Atzompa</t>
         </is>
       </c>
       <c r="C349">
@@ -4991,9 +6641,14 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>SAN MARTÍN TEXMELUCAN</t>
+          <t>San Martín Texmelucan</t>
         </is>
       </c>
       <c r="C350">
@@ -5004,9 +6659,14 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>SAN MARTÍN TOTOLTEPEC</t>
+          <t>San Martín Totoltepec</t>
         </is>
       </c>
       <c r="C351">
@@ -5017,9 +6677,14 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>SAN MATÍAS TLALANCALECA</t>
+          <t>San Matías Tlalancaleca</t>
         </is>
       </c>
       <c r="C352">
@@ -5030,9 +6695,14 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>SAN PEDRO CHOLULA</t>
+          <t>San Pedro Cholula</t>
         </is>
       </c>
       <c r="C353">
@@ -5043,9 +6713,14 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>SAN PEDRO YELOIXTLAHUACA</t>
+          <t>San Pedro Yeloixtlahuaca</t>
         </is>
       </c>
       <c r="C354">
@@ -5056,9 +6731,14 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>SAN SALVADOR EL SECO</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C355">
@@ -5069,9 +6749,14 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>SAN SALVADOR EL VERDE</t>
+          <t>San Salvador El Verde</t>
         </is>
       </c>
       <c r="C356">
@@ -5082,9 +6767,14 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>SANTA INÉS AHUATEMPAN</t>
+          <t>Santa Inés Ahuatempan</t>
         </is>
       </c>
       <c r="C357">
@@ -5095,9 +6785,14 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>SANTA ISABEL CHOLULA</t>
+          <t>Santa Isabel Cholula</t>
         </is>
       </c>
       <c r="C358">
@@ -5108,9 +6803,14 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SANTIAGO MIAHUATLÁN</t>
+          <t>Santiago Miahuatlán</t>
         </is>
       </c>
       <c r="C359">
@@ -5121,9 +6821,14 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>SANTO TOMÁS HUEYOTLIPAN</t>
+          <t>Santo Tomás Hueyotlipan</t>
         </is>
       </c>
       <c r="C360">
@@ -5134,9 +6839,14 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>TECALI DE HERRERA</t>
+          <t>Tecali De Herrera</t>
         </is>
       </c>
       <c r="C361">
@@ -5147,9 +6857,14 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>TECAMACHALCO</t>
+          <t>Tecamachalco</t>
         </is>
       </c>
       <c r="C362">
@@ -5160,9 +6875,14 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>TECOMATLÁN</t>
+          <t>Tecomatlán</t>
         </is>
       </c>
       <c r="C363">
@@ -5173,9 +6893,14 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>TEHUACÁN</t>
+          <t>Tehuacán</t>
         </is>
       </c>
       <c r="C364">
@@ -5186,9 +6911,14 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>TEHUITZINGO</t>
+          <t>Tehuitzingo</t>
         </is>
       </c>
       <c r="C365">
@@ -5199,9 +6929,14 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>TEOPANTLÁN</t>
+          <t>Teopantlán</t>
         </is>
       </c>
       <c r="C366">
@@ -5212,9 +6947,14 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>TEPEACA</t>
+          <t>Tepeaca</t>
         </is>
       </c>
       <c r="C367">
@@ -5225,9 +6965,14 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>TEPEOJUMA</t>
+          <t>Tepeojuma</t>
         </is>
       </c>
       <c r="C368">
@@ -5238,9 +6983,14 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>TEPEXI DE RODRÍGUEZ</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C369">
@@ -5251,9 +7001,14 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>TEZIUTLÁN</t>
+          <t>Teziutlán</t>
         </is>
       </c>
       <c r="C370">
@@ -5264,9 +7019,14 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>TIANGUISMANALCO</t>
+          <t>Tianguismanalco</t>
         </is>
       </c>
       <c r="C371">
@@ -5277,9 +7037,14 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>TILAPA</t>
+          <t>Tilapa</t>
         </is>
       </c>
       <c r="C372">
@@ -5290,9 +7055,14 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>TLACOTEPEC DE BENITO JUÁREZ</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C373">
@@ -5303,9 +7073,14 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>TLAHUAPAN</t>
+          <t>Tlahuapan</t>
         </is>
       </c>
       <c r="C374">
@@ -5316,9 +7091,14 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>TLAOLA</t>
+          <t>Tlaola</t>
         </is>
       </c>
       <c r="C375">
@@ -5329,9 +7109,14 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>TLAPANALÁ</t>
+          <t>Tlapanalá</t>
         </is>
       </c>
       <c r="C376">
@@ -5342,9 +7127,14 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>TLATLAUQUITEPEC</t>
+          <t>Tlatlauquitepec</t>
         </is>
       </c>
       <c r="C377">
@@ -5355,9 +7145,14 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>TLAXCO</t>
+          <t>Tlaxco</t>
         </is>
       </c>
       <c r="C378">
@@ -5368,9 +7163,14 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>TOCHIMILCO</t>
+          <t>Tochimilco</t>
         </is>
       </c>
       <c r="C379">
@@ -5381,9 +7181,14 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>TOCHTEPEC</t>
+          <t>Tochtepec</t>
         </is>
       </c>
       <c r="C380">
@@ -5394,9 +7199,14 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>TULCINGO</t>
+          <t>Tulcingo</t>
         </is>
       </c>
       <c r="C381">
@@ -5407,9 +7217,14 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>XICOTEPEC</t>
+          <t>Xicotepec</t>
         </is>
       </c>
       <c r="C382">
@@ -5420,9 +7235,14 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>XICOTLÁN</t>
+          <t>Xicotlán</t>
         </is>
       </c>
       <c r="C383">
@@ -5433,9 +7253,14 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>XOCHILTEPEC</t>
+          <t>Xochiltepec</t>
         </is>
       </c>
       <c r="C384">
@@ -5446,9 +7271,14 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>YEHUALTEPEC</t>
+          <t>Yehualtepec</t>
         </is>
       </c>
       <c r="C385">
@@ -5459,9 +7289,14 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>ZACAPOAXTLA</t>
+          <t>Zacapoaxtla</t>
         </is>
       </c>
       <c r="C386">
@@ -5472,9 +7307,14 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>ZACATLÁN</t>
+          <t>Zacatlán</t>
         </is>
       </c>
       <c r="C387">
@@ -5485,9 +7325,14 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="C388">
@@ -5498,9 +7343,14 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>ZIHUATEUTLA</t>
+          <t>Zihuateutla</t>
         </is>
       </c>
       <c r="C389">
@@ -5511,9 +7361,14 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>ZINACATEPEC</t>
+          <t>Zinacatepec</t>
         </is>
       </c>
       <c r="C390">
@@ -5524,9 +7379,14 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C391">
@@ -5539,12 +7399,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>ARROYO SECO</t>
+          <t>Arroyo Seco</t>
         </is>
       </c>
       <c r="C392">
@@ -5555,9 +7415,14 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>CADEREYTA DE MONTES</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C393">
@@ -5568,9 +7433,14 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>COLÓN</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="C394">
@@ -5581,9 +7451,14 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>EL MARQUÉS</t>
+          <t>El Marqués</t>
         </is>
       </c>
       <c r="C395">
@@ -5594,9 +7469,14 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PINAL DE AMOLES</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C396">
@@ -5607,9 +7487,14 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="C397">
@@ -5620,9 +7505,14 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>SAN JUAN DEL RÍO</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C398">
@@ -5633,9 +7523,14 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C399">
@@ -5648,12 +7543,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>QUINTANA ROO</t>
+          <t>Quintana Roo</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>OTHÓN P. BLANCO</t>
+          <t>Othón P. Blanco</t>
         </is>
       </c>
       <c r="C400">
@@ -5664,9 +7559,14 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C401">
@@ -5679,12 +7579,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>CIUDAD DEL MAÍZ</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C402">
@@ -5695,9 +7595,14 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>CIUDAD VALLES</t>
+          <t>Ciudad Valles</t>
         </is>
       </c>
       <c r="C403">
@@ -5708,9 +7613,14 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>EBANO</t>
+          <t>Ebano</t>
         </is>
       </c>
       <c r="C404">
@@ -5721,9 +7631,14 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MEXQUITIC DE CARMONA</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C405">
@@ -5734,9 +7649,14 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>RAYÓN</t>
+          <t>Rayón</t>
         </is>
       </c>
       <c r="C406">
@@ -5747,9 +7667,14 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="C407">
@@ -5760,9 +7685,14 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>TANQUIÁN DE ESCOBEDO</t>
+          <t>Tanquián De Escobedo</t>
         </is>
       </c>
       <c r="C408">
@@ -5773,9 +7703,14 @@
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>VANEGAS</t>
+          <t>Vanegas</t>
         </is>
       </c>
       <c r="C409">
@@ -5786,9 +7721,14 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>VILLA DE REYES</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C410">
@@ -5799,9 +7739,14 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C411">
@@ -5814,12 +7759,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>SINALOA</t>
+          <t>Sinaloa</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>BADIRAGUATO</t>
+          <t>Badiraguato</t>
         </is>
       </c>
       <c r="C412">
@@ -5830,9 +7775,14 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CULIACÁN</t>
+          <t>Culiacán</t>
         </is>
       </c>
       <c r="C413">
@@ -5843,9 +7793,14 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>ELOTA</t>
+          <t>Elota</t>
         </is>
       </c>
       <c r="C414">
@@ -5856,9 +7811,14 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>MAZATLÁN</t>
+          <t>Mazatlán</t>
         </is>
       </c>
       <c r="C415">
@@ -5869,9 +7829,14 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C416">
@@ -5884,12 +7849,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>SONORA</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>ALAMOS</t>
+          <t>Alamos</t>
         </is>
       </c>
       <c r="C417">
@@ -5900,9 +7865,14 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C418">
@@ -5915,12 +7885,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>TABASCO</t>
+          <t>Tabasco</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="C419">
@@ -5931,9 +7901,14 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>HUIMANGUILLO</t>
+          <t>Huimanguillo</t>
         </is>
       </c>
       <c r="C420">
@@ -5944,9 +7919,14 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>JALPA DE MÉNDEZ</t>
+          <t>Jalpa De Méndez</t>
         </is>
       </c>
       <c r="C421">
@@ -5957,9 +7937,14 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>TENOSIQUE</t>
+          <t>Tenosique</t>
         </is>
       </c>
       <c r="C422">
@@ -5970,9 +7955,14 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C423">
@@ -5985,12 +7975,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>TAMAULIPAS</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>BUSTAMANTE</t>
+          <t>Bustamante</t>
         </is>
       </c>
       <c r="C424">
@@ -6001,9 +7991,14 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>CIUDAD MADERO</t>
+          <t>Ciudad Madero</t>
         </is>
       </c>
       <c r="C425">
@@ -6014,9 +8009,14 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>EL MANTE</t>
+          <t>El Mante</t>
         </is>
       </c>
       <c r="C426">
@@ -6027,9 +8027,14 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>MATAMOROS</t>
+          <t>Matamoros</t>
         </is>
       </c>
       <c r="C427">
@@ -6040,9 +8045,14 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>NUEVO LAREDO</t>
+          <t>Nuevo Laredo</t>
         </is>
       </c>
       <c r="C428">
@@ -6053,9 +8063,14 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>TAMPICO</t>
+          <t>Tampico</t>
         </is>
       </c>
       <c r="C429">
@@ -6066,9 +8081,14 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C430">
@@ -6081,12 +8101,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>TLAXCALA</t>
+          <t>Tlaxcala</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>APETATITLÁN DE ANTONIO CARVAJAL</t>
+          <t>Apetatitlán De Antonio Carvajal</t>
         </is>
       </c>
       <c r="C431">
@@ -6097,9 +8117,14 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>APIZACO</t>
+          <t>Apizaco</t>
         </is>
       </c>
       <c r="C432">
@@ -6110,9 +8135,14 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>CALPULALPAN</t>
+          <t>Calpulalpan</t>
         </is>
       </c>
       <c r="C433">
@@ -6123,9 +8153,14 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>CHIAUTEMPAN</t>
+          <t>Chiautempan</t>
         </is>
       </c>
       <c r="C434">
@@ -6136,9 +8171,14 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>CONTLA DE JUAN CUAMATZI</t>
+          <t>Contla De Juan Cuamatzi</t>
         </is>
       </c>
       <c r="C435">
@@ -6149,9 +8189,14 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>HUAMANTLA</t>
+          <t>Huamantla</t>
         </is>
       </c>
       <c r="C436">
@@ -6162,9 +8207,14 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>HUEYOTLIPAN</t>
+          <t>Hueyotlipan</t>
         </is>
       </c>
       <c r="C437">
@@ -6175,9 +8225,14 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>IXTACUIXTLA DE MARIANO MATAMOROS</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C438">
@@ -6188,9 +8243,14 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>LA MAGDALENA TLALTELULCO</t>
+          <t>La Magdalena Tlaltelulco</t>
         </is>
       </c>
       <c r="C439">
@@ -6201,9 +8261,14 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>MAZATECOCHCO DE JOSÉ MARÍA MORELOS</t>
+          <t>Mazatecochco De José María Morelos</t>
         </is>
       </c>
       <c r="C440">
@@ -6214,9 +8279,14 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>NATÍVITAS</t>
+          <t>Natívitas</t>
         </is>
       </c>
       <c r="C441">
@@ -6227,9 +8297,14 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>NO SE REGISTRÓ EL MUNICIPIO/CONDADO/ALCALDÍA DE NACIMIENTO</t>
+          <t>No Se Registró El Municipio/Condado/Alcaldía De Nacimiento</t>
         </is>
       </c>
       <c r="C442">
@@ -6240,9 +8315,14 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>PAPALOTLA DE XICOHTÉNCATL</t>
+          <t>Papalotla De Xicohténcatl</t>
         </is>
       </c>
       <c r="C443">
@@ -6253,9 +8333,14 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SAN DAMIÁN TEXÓLOC</t>
+          <t>San Damián Texóloc</t>
         </is>
       </c>
       <c r="C444">
@@ -6266,9 +8351,14 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO TETLANOHCAN</t>
+          <t>San Francisco Tetlanohcan</t>
         </is>
       </c>
       <c r="C445">
@@ -6279,9 +8369,14 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>SAN JERÓNIMO ZACUALPAN</t>
+          <t>San Jerónimo Zacualpan</t>
         </is>
       </c>
       <c r="C446">
@@ -6292,9 +8387,14 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>SAN JUAN HUACTZINCO</t>
+          <t>San Juan Huactzinco</t>
         </is>
       </c>
       <c r="C447">
@@ -6305,9 +8405,14 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SAN PABLO DEL MONTE</t>
+          <t>San Pablo Del Monte</t>
         </is>
       </c>
       <c r="C448">
@@ -6318,9 +8423,14 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>SANTA APOLONIA TEACALCO</t>
+          <t>Santa Apolonia Teacalco</t>
         </is>
       </c>
       <c r="C449">
@@ -6331,9 +8441,14 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>SANTA CATARINA AYOMETLA</t>
+          <t>Santa Catarina Ayometla</t>
         </is>
       </c>
       <c r="C450">
@@ -6344,9 +8459,14 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>TENANCINGO</t>
+          <t>Tenancingo</t>
         </is>
       </c>
       <c r="C451">
@@ -6357,9 +8477,14 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>TEOLOCHOLCO</t>
+          <t>Teolocholco</t>
         </is>
       </c>
       <c r="C452">
@@ -6370,9 +8495,14 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>TEPEYANCO</t>
+          <t>Tepeyanco</t>
         </is>
       </c>
       <c r="C453">
@@ -6383,9 +8513,14 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>TERRENATE</t>
+          <t>Terrenate</t>
         </is>
       </c>
       <c r="C454">
@@ -6396,9 +8531,14 @@
       </c>
     </row>
     <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>TETLA DE LA SOLIDARIDAD</t>
+          <t>Tetla De La Solidaridad</t>
         </is>
       </c>
       <c r="C455">
@@ -6409,9 +8549,14 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>TETLATLAHUCA</t>
+          <t>Tetlatlahuca</t>
         </is>
       </c>
       <c r="C456">
@@ -6422,9 +8567,14 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>TLAXCALA</t>
+          <t>Tlaxcala</t>
         </is>
       </c>
       <c r="C457">
@@ -6435,9 +8585,14 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>TLAXCO</t>
+          <t>Tlaxco</t>
         </is>
       </c>
       <c r="C458">
@@ -6448,9 +8603,14 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>XICOHTZINCO</t>
+          <t>Xicohtzinco</t>
         </is>
       </c>
       <c r="C459">
@@ -6461,9 +8621,14 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>ZACATELCO</t>
+          <t>Zacatelco</t>
         </is>
       </c>
       <c r="C460">
@@ -6474,9 +8639,14 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C461">
@@ -6489,12 +8659,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>ACAYUCAN</t>
+          <t>Acayucan</t>
         </is>
       </c>
       <c r="C462">
@@ -6505,9 +8675,14 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>ACTOPAN</t>
+          <t>Actopan</t>
         </is>
       </c>
       <c r="C463">
@@ -6518,9 +8693,14 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>ALTO LUCERO DE GUTIÉRREZ BARRIOS</t>
+          <t>Alto Lucero De Gutiérrez Barrios</t>
         </is>
       </c>
       <c r="C464">
@@ -6531,9 +8711,14 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>ATZALAN</t>
+          <t>Atzalan</t>
         </is>
       </c>
       <c r="C465">
@@ -6544,9 +8729,14 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>BANDERILLA</t>
+          <t>Banderilla</t>
         </is>
       </c>
       <c r="C466">
@@ -6557,9 +8747,14 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>CATEMACO</t>
+          <t>Catemaco</t>
         </is>
       </c>
       <c r="C467">
@@ -6570,9 +8765,14 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>CHICONAMEL</t>
+          <t>Chiconamel</t>
         </is>
       </c>
       <c r="C468">
@@ -6583,9 +8783,14 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>CHICONTEPEC</t>
+          <t>Chicontepec</t>
         </is>
       </c>
       <c r="C469">
@@ -6596,9 +8801,14 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>COATZACOALCOS</t>
+          <t>Coatzacoalcos</t>
         </is>
       </c>
       <c r="C470">
@@ -6609,9 +8819,14 @@
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>COSCOMATEPEC</t>
+          <t>Coscomatepec</t>
         </is>
       </c>
       <c r="C471">
@@ -6622,9 +8837,14 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>COYUTLA</t>
+          <t>Coyutla</t>
         </is>
       </c>
       <c r="C472">
@@ -6635,9 +8855,14 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>CUITLÁHUAC</t>
+          <t>Cuitláhuac</t>
         </is>
       </c>
       <c r="C473">
@@ -6648,9 +8873,14 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>CÓRDOBA</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="C474">
@@ -6661,9 +8891,14 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>Espinal</t>
         </is>
       </c>
       <c r="C475">
@@ -6674,9 +8909,14 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>HIDALGOTITLÁN</t>
+          <t>Hidalgotitlán</t>
         </is>
       </c>
       <c r="C476">
@@ -6687,9 +8927,14 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>HUATUSCO</t>
+          <t>Huatusco</t>
         </is>
       </c>
       <c r="C477">
@@ -6700,9 +8945,14 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>IGNACIO DE LA LLAVE</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C478">
@@ -6713,9 +8963,14 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>IXHUATLÁN DE MADERO</t>
+          <t>Ixhuatlán De Madero</t>
         </is>
       </c>
       <c r="C479">
@@ -6726,9 +8981,14 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>JESÚS CARRANZA</t>
+          <t>Jesús Carranza</t>
         </is>
       </c>
       <c r="C480">
@@ -6739,9 +8999,14 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>JOSÉ AZUETA</t>
+          <t>José Azueta</t>
         </is>
       </c>
       <c r="C481">
@@ -6752,9 +9017,14 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>JUCHIQUE DE FERRER</t>
+          <t>Juchique De Ferrer</t>
         </is>
       </c>
       <c r="C482">
@@ -6765,9 +9035,14 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>LA ANTIGUA</t>
+          <t>La Antigua</t>
         </is>
       </c>
       <c r="C483">
@@ -6778,9 +9053,14 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>LAS CHOAPAS</t>
+          <t>Las Choapas</t>
         </is>
       </c>
       <c r="C484">
@@ -6791,9 +9071,14 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>MARTÍNEZ DE LA TORRE</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C485">
@@ -6804,9 +9089,14 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>MINATITLÁN</t>
+          <t>Minatitlán</t>
         </is>
       </c>
       <c r="C486">
@@ -6817,9 +9107,14 @@
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>NANCHITAL DE LÁZARO CÁRDENAS DEL RÍO</t>
+          <t>Nanchital De Lázaro Cárdenas Del Río</t>
         </is>
       </c>
       <c r="C487">
@@ -6830,9 +9125,14 @@
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>OMEALCA</t>
+          <t>Omealca</t>
         </is>
       </c>
       <c r="C488">
@@ -6843,9 +9143,14 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>ORIZABA</t>
+          <t>Orizaba</t>
         </is>
       </c>
       <c r="C489">
@@ -6856,9 +9161,14 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>PAPANTLA</t>
+          <t>Papantla</t>
         </is>
       </c>
       <c r="C490">
@@ -6869,9 +9179,14 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>PASO DE OVEJAS</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C491">
@@ -6882,9 +9197,14 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>PLAYA VICENTE</t>
+          <t>Playa Vicente</t>
         </is>
       </c>
       <c r="C492">
@@ -6895,9 +9215,14 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>POZA RICA DE HIDALGO</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C493">
@@ -6908,9 +9233,14 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>PÁNUCO</t>
+          <t>Pánuco</t>
         </is>
       </c>
       <c r="C494">
@@ -6921,9 +9251,14 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS TUXTLA</t>
+          <t>San Andrés Tuxtla</t>
         </is>
       </c>
       <c r="C495">
@@ -6934,9 +9269,14 @@
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>SAN JUAN EVANGELISTA</t>
+          <t>San Juan Evangelista</t>
         </is>
       </c>
       <c r="C496">
@@ -6947,9 +9287,14 @@
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>TANTOYUCA</t>
+          <t>Tantoyuca</t>
         </is>
       </c>
       <c r="C497">
@@ -6960,9 +9305,14 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>TEXCATEPEC</t>
+          <t>Texcatepec</t>
         </is>
       </c>
       <c r="C498">
@@ -6973,9 +9323,14 @@
       </c>
     </row>
     <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>TEZONAPA</t>
+          <t>Tezonapa</t>
         </is>
       </c>
       <c r="C499">
@@ -6986,9 +9341,14 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>TIERRA BLANCA</t>
+          <t>Tierra Blanca</t>
         </is>
       </c>
       <c r="C500">
@@ -6999,9 +9359,14 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>TLALIXCOYAN</t>
+          <t>Tlalixcoyan</t>
         </is>
       </c>
       <c r="C501">
@@ -7012,9 +9377,14 @@
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>TOMATLÁN</t>
+          <t>Tomatlán</t>
         </is>
       </c>
       <c r="C502">
@@ -7025,9 +9395,14 @@
       </c>
     </row>
     <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>TUXPAN</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C503">
@@ -7038,9 +9413,14 @@
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>URSULO GALVÁN</t>
+          <t>Ursulo Galván</t>
         </is>
       </c>
       <c r="C504">
@@ -7051,9 +9431,14 @@
       </c>
     </row>
     <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>VERACRUZ</t>
+          <t>Veracruz</t>
         </is>
       </c>
       <c r="C505">
@@ -7064,9 +9449,14 @@
       </c>
     </row>
     <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>XALAPA</t>
+          <t>Xalapa</t>
         </is>
       </c>
       <c r="C506">
@@ -7077,9 +9467,14 @@
       </c>
     </row>
     <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>YANGA</t>
+          <t>Yanga</t>
         </is>
       </c>
       <c r="C507">
@@ -7090,9 +9485,14 @@
       </c>
     </row>
     <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>ÁLAMO TEMAPACHE</t>
+          <t>Álamo Temapache</t>
         </is>
       </c>
       <c r="C508">
@@ -7103,9 +9503,14 @@
       </c>
     </row>
     <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C509">
@@ -7118,12 +9523,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>YUCATÁN</t>
+          <t>Yucatán</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>IZAMAL</t>
+          <t>Izamal</t>
         </is>
       </c>
       <c r="C510">
@@ -7134,9 +9539,14 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C511">
@@ -7149,12 +9559,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>GENERAL PÁNFILO NATERA</t>
+          <t>General Pánfilo Natera</t>
         </is>
       </c>
       <c r="C512">
@@ -7165,9 +9575,14 @@
       </c>
     </row>
     <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>OJOCALIENTE</t>
+          <t>Ojocaliente</t>
         </is>
       </c>
       <c r="C513">
@@ -7178,9 +9593,14 @@
       </c>
     </row>
     <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>PINOS</t>
+          <t>Pinos</t>
         </is>
       </c>
       <c r="C514">
@@ -7191,9 +9611,14 @@
       </c>
     </row>
     <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>TEÚL DE GONZÁLEZ ORTEGA</t>
+          <t>Teúl De González Ortega</t>
         </is>
       </c>
       <c r="C515">
@@ -7204,9 +9629,14 @@
       </c>
     </row>
     <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>TLALTENANGO DE SÁNCHEZ ROMÁN</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C516">
@@ -7217,9 +9647,14 @@
       </c>
     </row>
     <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>VILLA DE COS</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C517">
@@ -7230,9 +9665,14 @@
       </c>
     </row>
     <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>VILLA GONZÁLEZ ORTEGA</t>
+          <t>Villa González Ortega</t>
         </is>
       </c>
       <c r="C518">
@@ -7243,9 +9683,14 @@
       </c>
     </row>
     <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>Villanueva</t>
         </is>
       </c>
       <c r="C519">
@@ -7256,9 +9701,14 @@
       </c>
     </row>
     <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C520">
@@ -7271,7 +9721,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C521">
@@ -7279,41 +9729,6 @@
       </c>
       <c r="D521">
         <v>1</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
